--- a/artfynd/A 72111-2021 artfynd.xlsx
+++ b/artfynd/A 72111-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72111-2021 artfynd.xlsx
+++ b/artfynd/A 72111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3929273</v>
+        <v>134427</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södertorp NNV, Upl</t>
+          <t>Södertorp N 230 m, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684263.3359823982</v>
+        <v>684258</v>
       </c>
       <c r="R2" t="n">
-        <v>6628467.44490732</v>
+        <v>6628366</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +744,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fasterna</t>
+          <t>Rimbo</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>återfynd, 2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Örtrik granskog</t>
+          <t>Olikåldrig luckig gammal granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,53 +791,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2219898</v>
+        <v>16708794</v>
       </c>
       <c r="B3" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södertorp NNV, Upl</t>
+          <t>Södertorp NO, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684263.3359823982</v>
+        <v>684232</v>
       </c>
       <c r="R3" t="n">
-        <v>6628467.44490732</v>
+        <v>6628409</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,27 +855,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Fasterna</t>
+          <t>Rimbo</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +879,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Örtrik granskog</t>
+          <t>Olikåldrig luckig gammal granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,50 +897,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5047440</v>
+        <v>183645</v>
       </c>
       <c r="B4" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>655</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södertorp NNV, Upl</t>
+          <t>Södertorp N 300 m, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684263.3359823982</v>
+        <v>684204</v>
       </c>
       <c r="R4" t="n">
-        <v>6628467.44490732</v>
+        <v>6628479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,27 +966,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Fasterna</t>
+          <t>Rimbo</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-06-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +995,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Örtrik granskog</t>
+          <t>På gammal grov ek i granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,62 +1018,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1936083</v>
+        <v>84610412</v>
       </c>
       <c r="B5" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1444</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erlandsholm SSV, Upl</t>
+          <t>Södertorpet, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684152.3949761286</v>
+        <v>684299</v>
       </c>
       <c r="R5" t="n">
-        <v>6628624.985970937</v>
+        <v>6628152</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,27 +1082,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fasterna</t>
+          <t>Rimbo</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-06-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-06-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,17 +1101,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lövrik granskog i liten nordsluttning</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2 gamla levande aspar</t>
+          <t>Skogsbryn</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,57 +1125,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84610412</v>
+        <v>1936083</v>
       </c>
       <c r="B6" t="n">
-        <v>81961</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1444</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södertorpet, Upl</t>
+          <t>Erlandsholm SSV, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684299.1682294135</v>
+        <v>684152</v>
       </c>
       <c r="R6" t="n">
-        <v>6628152.219681954</v>
+        <v>6628625</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,27 +1194,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Rimbo</t>
+          <t>Fasterna</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,13 +1213,17 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skogsbryn</t>
+          <t>Lövrik granskog i liten nordsluttning</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2 gamla levande aspar</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,19 +1241,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84610367</v>
+        <v>2219898</v>
       </c>
       <c r="B7" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1312,34 +1269,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södertorpet, Upl</t>
+          <t>Södertorp NNV, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684299.1682294135</v>
+        <v>684263</v>
       </c>
       <c r="R7" t="n">
-        <v>6628152.219681954</v>
+        <v>6628467</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,27 +1301,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Rimbo</t>
+          <t>Fasterna</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1325,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Skogsbryn</t>
+          <t>Örtrik granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1407,6 +1340,445 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81631285</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södertorp N 300 m, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>684204</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628479</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>84610367</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södertorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>684299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6628152</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-03-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-03-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3929273</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södertorp NNV, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>684263</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6628467</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2009-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2009-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5047440</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södertorp NNV, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>684263</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6628467</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2009-06-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2009-06-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 72111-2021 artfynd.xlsx
+++ b/artfynd/A 72111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16708794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/183645</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84610412</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1936083</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2219898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81631285</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84610367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3929273</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,8 +1829,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5047440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>